--- a/per-stock/CIFR/financials.xlsx
+++ b/per-stock/CIFR/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8315970048</v>
+        <v>11936055296</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12373133312</v>
+        <v>15993219072</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -578,7 +587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43.255318</v>
+        <v>43.55224</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -593,7 +602,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39.63364</v>
+        <v>56.88685</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -713,11 +722,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-2948059648</v>
+        <v>-1017369000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -743,7 +752,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>20.33</v>
+        <v>29.18</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -787,6 +796,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D51</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C51</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B51</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B48:E48)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D49</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C49</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B49</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B46:E46)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D40</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C40</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B40</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B38:E38)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B7:E7)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B5</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1785,7 +2265,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2943,7 +3423,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4525,7 +5005,1911 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H80"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>7346254</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>7111468</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>1885843</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>1365042</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>455899</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>405266365</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>404963061</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>393602553</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>386758546</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>370857699</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>412612619</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>412074529</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>395488396</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>388123588</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>371313598</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>4016906000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>2121178000</v>
+      </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n">
+        <v>104409000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>12286000</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>26745000</v>
+      </c>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>4746687000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>2767048000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1043976000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>189288000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>58383000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>637028000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>728147000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>773770000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>739675000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>725752000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>5446296000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>3554976000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1806270000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>916017000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>770254000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>2648295000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1953788000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>849232000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>167157000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>15816000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>637028000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>728147000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>773770000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>739675000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>725752000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>14578000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>17607000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>20901000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>22175000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>22924000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>714187000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>805535000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>783195000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>748904000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>734795000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>5090948000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>3517183000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>1806270000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>916017000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>734795000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>739866000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>835854000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>783195000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>748904000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>734795000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Minority Interest</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>25679000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>30319000</v>
+      </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>714187000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>805535000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>783195000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>748904000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>734795000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>-1117972000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>-1003656000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>-269451000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-266168000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>-220387000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>1831753000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>1808786000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>1052253000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>1014686000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>954812000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>413000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>412000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>395000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>388000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>371000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>413000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>412000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>395000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>388000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>371000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>5653719000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>3456054000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>2057671000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>269855000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>178997000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>4408020000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>2756983000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1487424000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>217349000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>40256000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Derivative Product Liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n">
+        <v>414320000</v>
+      </c>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>3871000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>3406000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>3634000</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>4269000</v>
+      </c>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>3871000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>3406000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>3634000</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>4269000</v>
+      </c>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>4385083000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>2723287000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1036330000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>181833000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>15821000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>8322000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>11639000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>13255000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>14720000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>15821000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>4376761000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>2711648000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1023075000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>167113000</v>
+      </c>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Long Term Provisions</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>22937000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>33696000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>32903000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>32110000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>20801000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>1245699000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>699071000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>570247000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>52506000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>138741000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>497032000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>540500000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>512590000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>907000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>487000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>7447000</v>
+      </c>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>7447000</v>
+      </c>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>361604000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>43761000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>7646000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>7455000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>42562000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>6256000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>5968000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>7646000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>7455000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>7103000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>355348000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>37793000</v>
+      </c>
+      <c r="D38" s="3" t="n"/>
+      <c r="E38" s="3" t="n"/>
+      <c r="F38" s="3" t="n">
+        <v>35459000</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>32330000</v>
+      </c>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>355348000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>37793000</v>
+      </c>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n">
+        <v>10459000</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>7300000</v>
+      </c>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Line Of Credit</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>32330000</v>
+      </c>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>5847000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>6697000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>4257000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>3407000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>376616000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>108963000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>43314000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>40794000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>92772000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>169632000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>59589000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>18845000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>9723000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>39831000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Interest Payable</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>65601000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>16892000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>1412000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>907000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>487000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>206984000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>49374000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>24469000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>31071000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>52941000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Other Payable</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n">
+        <v>8297000</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>8297000</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>8297000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>9065000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>9310000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>12007000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>16200000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>14765000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>197919000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>40064000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>12462000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>14871000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>29879000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>6393585000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>4291908000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>2840866000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>1018759000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>913792000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>2499591000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>1639049000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>1421387000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>799096000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>759235000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>1072781000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>837071000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>566537000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>19078000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>19086000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Non Current Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>27755000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>27732000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>12045000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>13794000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>19776000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Financial Assets</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>6940000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>22720000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>121664000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>41891000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>50165000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>29400000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>42289000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>45901000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>48499000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Long Term Equity Investment</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>29400000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>42289000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>45901000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>48499000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>77159000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>77388000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>9425000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>9229000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>9043000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>77159000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>77388000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>9425000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>9229000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>9043000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>1314956000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>644738000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>669427000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>669203000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>612666000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>-226756000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>-334165000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>-301857000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>-243568000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>-200245000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>1541712000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>978903000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>971284000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>912771000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>812911000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>121746000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>134122000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>151109000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>149867000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>137582000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>922216000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>287432000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>19784000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>194957000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>242736000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>104152000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>122021000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>119437000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>115038000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>40969000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n"/>
+      <c r="C64" s="3" t="n"/>
+      <c r="D64" s="3" t="n"/>
+      <c r="E64" s="3" t="n"/>
+      <c r="F64" s="3" t="n">
+        <v>340327000</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>342111000</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>433000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>66990000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>66594000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>65736000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>53104000</v>
+      </c>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>131180000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>79054000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>58330000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>58330000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>51297000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>195428000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>289680000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>556888000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>341475000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>340327000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>3893994000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>2652859000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>1419479000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>219663000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>154557000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>29873000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>7977000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>3966000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>7417000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>2970000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Hedging Assets Current</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>21640000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>34090000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>36766000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>35629000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>42835000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Assets Held For Sale Current</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>30767000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>94879000</v>
+      </c>
+      <c r="D71" s="3" t="n"/>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Restricted Cash</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>3011874000</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>1761292000</v>
+      </c>
+      <c r="D72" s="3" t="n"/>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>76150000</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>125400000</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>170303000</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>112089000</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>52024000</v>
+      </c>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>76150000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>125400000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>170303000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>112089000</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>52024000</v>
+      </c>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>8487000</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>958000</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>1004000</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>1824000</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>33555000</v>
+      </c>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n"/>
+      <c r="C76" s="3" t="n"/>
+      <c r="D76" s="3" t="n"/>
+      <c r="E76" s="3" t="n"/>
+      <c r="F76" s="3" t="n">
+        <v>32497000</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>32248000</v>
+      </c>
+      <c r="H76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Duefrom Related Parties Current</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>271000</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>308000</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>249000</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>8487000</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>687000</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>696000</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>758000</v>
+      </c>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>715203000</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>628263000</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>1207440000</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>62704000</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>23173000</v>
+      </c>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>715203000</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>628263000</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>1207440000</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>62704000</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>23173000</v>
+      </c>
+      <c r="G80" s="3" t="n"/>
+      <c r="H80" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5733,7 +8117,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7209,7 +9593,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
